--- a/data/plages_horaires.xlsx
+++ b/data/plages_horaires.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,16 +456,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -476,21 +476,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -501,21 +501,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -526,17 +526,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -551,21 +551,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -576,21 +576,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -601,21 +601,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Vestiaire</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -626,21 +626,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -651,21 +651,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -676,21 +676,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -701,42 +701,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lundi</t>
+          <t>Mardi</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -756,16 +756,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -781,16 +781,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -801,17 +801,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -826,17 +826,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -851,21 +851,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -876,21 +876,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Vestiaire</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -901,21 +901,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -926,21 +926,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -951,21 +951,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -976,7 +976,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -996,51 +996,51 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mardi</t>
+          <t>Mercredi</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mardi</t>
+          <t>Mercredi</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1061,11 +1061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1081,16 +1081,16 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1126,21 +1126,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Vestiaire</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1186,11 +1186,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1201,21 +1201,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1251,67 +1251,67 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mercredi</t>
+          <t>Jeudi</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mercredi</t>
+          <t>Jeudi</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1321,26 +1321,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mercredi</t>
+          <t>Jeudi</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1351,17 +1351,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1376,17 +1376,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1406,16 +1406,16 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -1431,16 +1431,16 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1501,21 +1501,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1546,101 +1546,101 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jeudi</t>
+          <t>Vendredi</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Jeudi</t>
+          <t>Vendredi</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Jeudi</t>
+          <t>Vendredi</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Jeudi</t>
+          <t>Vendredi</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -1651,21 +1651,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1676,21 +1676,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Vestiaire</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1726,21 +1726,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1801,17 +1801,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -1821,126 +1821,126 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Vendredi</t>
+          <t>Samedi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Vendredi</t>
+          <t>Samedi</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Vendredi</t>
+          <t>Samedi</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Vendredi</t>
+          <t>Samedi</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Vendredi</t>
+          <t>Samedi</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1951,21 +1951,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -1976,17 +1976,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Vestiaire</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2001,17 +2001,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2026,21 +2026,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -2051,21 +2051,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2081,22 +2081,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Samedi</t>
+          <t>Dimanche</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2106,141 +2106,141 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Samedi</t>
+          <t>Dimanche</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Samedi</t>
+          <t>Dimanche</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Samedi</t>
+          <t>Dimanche</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Samedi</t>
+          <t>Dimanche</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Samedi</t>
+          <t>Dimanche</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -2251,21 +2251,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Vestiaire</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2286,11 +2286,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2326,21 +2326,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -2351,196 +2351,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Dimanche</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Technique</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Dimanche</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Accueil</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Dimanche</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Billetterie</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Dimanche</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Bar</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Dimanche</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Vestiaire</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Dimanche</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Sécurité</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Dimanche</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Technique</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/plages_horaires.xlsx
+++ b/data/plages_horaires.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sschies1\_code\1.09_VScode\06_VoeuxConcerts\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FB898E-1042-4252-BD9C-AEE6C2F59585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4A096C-D14C-4DC0-A681-57330BC763A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-69" yWindow="-69" windowWidth="22080" windowHeight="13132" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mardi" sheetId="2" r:id="rId1"/>
@@ -19,14 +19,27 @@
     <sheet name="Vendredi" sheetId="15" r:id="rId4"/>
     <sheet name="Samedi" sheetId="16" r:id="rId5"/>
     <sheet name="Dimanche" sheetId="17" r:id="rId6"/>
-    <sheet name="Tâches" sheetId="12" state="hidden" r:id="rId7"/>
+    <sheet name="Tâches" sheetId="12" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="39">
   <si>
     <t>Tâche</t>
   </si>
@@ -113,6 +126,36 @@
   </si>
   <si>
     <t>Tâches</t>
+  </si>
+  <si>
+    <t>Déambule Gerry</t>
+  </si>
+  <si>
+    <t>Déambule Colbok</t>
+  </si>
+  <si>
+    <t>Déambule Goulus</t>
+  </si>
+  <si>
+    <t>Déambule Ko-compagnie</t>
+  </si>
+  <si>
+    <t>Déambule Spoutnik</t>
+  </si>
+  <si>
+    <t>Déambule FBI</t>
+  </si>
+  <si>
+    <t>Accueil</t>
+  </si>
+  <si>
+    <t>Abeilles Ruche</t>
+  </si>
+  <si>
+    <t>Bourdon.ne</t>
+  </si>
+  <si>
+    <t>Horaires</t>
   </si>
 </sst>
 </file>
@@ -470,11 +513,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA866B2F-4C6D-48C1-B7B5-0E0D9D9973FA}">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="16.15234375" customWidth="1"/>
     <col min="2" max="3" width="9.23046875" style="4"/>
+    <col min="4" max="4" width="14.3828125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.4">
@@ -493,13 +537,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="B2" s="3">
-        <v>0.6875</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C2" s="3">
-        <v>0.75</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -507,69 +551,69 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="B3" s="3">
-        <v>0.75</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="C3" s="3">
-        <v>0.8125</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="B4" s="3">
-        <v>0.8125</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C4" s="3">
-        <v>0.875</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="B5" s="3">
-        <v>0.875</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="C5" s="3">
-        <v>0.9375</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="B6" s="3">
-        <v>0.9375</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="C6" s="3">
-        <v>1</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B7" s="3">
-        <v>0.6875</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C7" s="3">
-        <v>0.77083333333333337</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -577,13 +621,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B8" s="3">
-        <v>0.77083333333333337</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="C8" s="3">
-        <v>0.85416666666666663</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -591,16 +635,16 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B9" s="3">
-        <v>0.85416666666666663</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="C9" s="3">
-        <v>0.9375</v>
+        <v>1.0208333333333333</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -608,10 +652,10 @@
         <v>18</v>
       </c>
       <c r="B10" s="3">
-        <v>0.9375</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C10" s="3">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D10">
         <v>3</v>
@@ -619,13 +663,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B11" s="3">
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="C11" s="3">
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D11">
         <v>3</v>
@@ -633,13 +677,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B12" s="3">
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="C12" s="3">
-        <v>0.8125</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="D12">
         <v>3</v>
@@ -647,44 +691,44 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B13" s="3">
-        <v>0.8125</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="C13" s="3">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="3">
-        <v>0.875</v>
+        <v>0.6875</v>
       </c>
       <c r="C14" s="3">
-        <v>0.9375</v>
+        <v>0.75</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" s="3">
-        <v>0.9375</v>
+        <v>0.75</v>
       </c>
       <c r="C15" s="3">
-        <v>1</v>
+        <v>0.8125</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
@@ -692,10 +736,10 @@
         <v>20</v>
       </c>
       <c r="B16" s="3">
-        <v>0.6875</v>
+        <v>0.8125</v>
       </c>
       <c r="C16" s="3">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -706,10 +750,10 @@
         <v>20</v>
       </c>
       <c r="B17" s="3">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="C17" s="3">
-        <v>0.8125</v>
+        <v>0.9375</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -720,10 +764,10 @@
         <v>20</v>
       </c>
       <c r="B18" s="3">
-        <v>0.8125</v>
+        <v>0.9375</v>
       </c>
       <c r="C18" s="3">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -731,97 +775,97 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19" s="3">
-        <v>0.875</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C19" s="3">
-        <v>0.9375</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20" s="3">
-        <v>0.9375</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="C20" s="3">
-        <v>1</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B21" s="3">
-        <v>0.70833333333333337</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="C21" s="3">
-        <v>0.77083333333333337</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C22" s="3">
         <v>0.91666666666666663</v>
       </c>
-      <c r="C22" s="3">
-        <v>0.97916666666666663</v>
-      </c>
       <c r="D22">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="C23" s="3">
-        <v>0.875</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B24" s="3">
-        <v>0.77083333333333337</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="C24" s="3">
-        <v>0.8125</v>
+        <v>1.0208333333333333</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>6</v>
+        <v>37</v>
+      </c>
+      <c r="B25" s="3">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C25" s="3">
+        <v>0.79166666666666663</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -829,13 +873,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>11</v>
+        <v>37</v>
+      </c>
+      <c r="B26" s="3">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C26" s="3">
+        <v>0.91666666666666663</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -843,13 +887,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>13</v>
+        <v>37</v>
+      </c>
+      <c r="B27" s="3">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C27" s="3">
+        <v>1.0208333333333333</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -857,13 +901,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>4</v>
+        <v>19</v>
+      </c>
+      <c r="B28" s="3">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C28" s="3">
+        <v>0.72916666666666663</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -871,41 +915,41 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="B29" s="3">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0.79166666666666663</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>6</v>
+        <v>19</v>
+      </c>
+      <c r="B30" s="3">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C30" s="3">
+        <v>0.85416666666666663</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>4</v>
+        <v>19</v>
+      </c>
+      <c r="B31" s="3">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C31" s="3">
+        <v>0.91666666666666663</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -913,13 +957,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>25</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
+      </c>
+      <c r="B32" s="3">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C32" s="3">
+        <v>0.97916666666666663</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -927,13 +971,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>10</v>
+        <v>19</v>
+      </c>
+      <c r="B33" s="3">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="C33" s="3">
+        <v>1.0208333333333333</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -941,13 +985,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>26</v>
-      </c>
-      <c r="B34" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>9</v>
+      <c r="C34" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -955,48 +999,168 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>27</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>27</v>
-      </c>
-      <c r="B36" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>31</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>32</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>33</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>33</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>34</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{450BFCD5-BE43-4BC3-9510-EE5B8A7F1D61}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F8E24F13-6261-4BE2-B208-016A7D67164C}">
           <x14:formula1>
-            <xm:f>#REF!</xm:f>
+            <xm:f>Tâches!$A$2:$A$19</xm:f>
           </x14:formula1>
-          <xm:sqref>A37:A78</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0D9D36F4-820D-4267-B7D1-0CC3E863FE8F}">
-          <x14:formula1>
-            <xm:f>Tâches!$A$2:$A$15</xm:f>
-          </x14:formula1>
-          <xm:sqref>A2:A36</xm:sqref>
+          <xm:sqref>A2:A495</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1518,21 +1682,20 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A37:A78" xr:uid="{C25B69B0-91F1-48D4-9A26-063CBFB71866}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{681463FE-B2A4-41FC-B9CF-344DF7F46A27}">
           <x14:formula1>
-            <xm:f>Tâches!$A$2:$A$15</xm:f>
+            <xm:f>Tâches!$A$8:$A$15</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A36</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C25B69B0-91F1-48D4-9A26-063CBFB71866}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>A37:A78</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2054,19 +2217,18 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A37:A78" xr:uid="{C8078D9C-4113-42B8-B196-328FBD100CF1}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C8078D9C-4113-42B8-B196-328FBD100CF1}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>A37:A78</xm:sqref>
-        </x14:dataValidation>
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1E5801FF-69D3-4F42-90AD-4F59B8D30F8C}">
           <x14:formula1>
-            <xm:f>Tâches!$A$2:$A$15</xm:f>
+            <xm:f>Tâches!$A$8:$A$15</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A36</xm:sqref>
         </x14:dataValidation>
@@ -2590,21 +2752,20 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A37:A78" xr:uid="{D3B39F94-F6DE-4941-A391-81523627A908}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B631A0C4-531A-44AB-B9EA-B7D7E31D7251}">
           <x14:formula1>
-            <xm:f>Tâches!$A$2:$A$15</xm:f>
+            <xm:f>Tâches!$A$8:$A$15</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A36</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D3B39F94-F6DE-4941-A391-81523627A908}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>A37:A78</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3126,19 +3287,18 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A37:A78" xr:uid="{364F3D2D-E885-4785-9D64-6EB560CC2B15}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{364F3D2D-E885-4785-9D64-6EB560CC2B15}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>A37:A78</xm:sqref>
-        </x14:dataValidation>
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{47D4686B-0097-4A47-95B0-E31D35A9D5B5}">
           <x14:formula1>
-            <xm:f>Tâches!$A$2:$A$15</xm:f>
+            <xm:f>Tâches!$A$8:$A$15</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A36</xm:sqref>
         </x14:dataValidation>
@@ -3662,21 +3822,20 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A37:A78" xr:uid="{19CFD26A-4385-463F-8A11-84755CB33986}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D59E45ED-DF26-42E3-B55D-A2C4762E6F3A}">
           <x14:formula1>
-            <xm:f>Tâches!$A$2:$A$15</xm:f>
+            <xm:f>Tâches!$A$8:$A$15</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A36</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{19CFD26A-4385-463F-8A11-84755CB33986}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>A37:A78</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3686,10 +3845,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B30C51F-AE90-4524-AE2A-6A9EE13EB899}">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="17.15234375" customWidth="1"/>
+    <col min="1" max="1" width="25.23046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.4">
@@ -3699,17 +3858,17 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
@@ -3719,52 +3878,72 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/plages_horaires.xlsx
+++ b/data/plages_horaires.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sschies1\_code\1.09_VScode\06_VoeuxConcerts\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4A096C-D14C-4DC0-A681-57330BC763A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C79058-9936-4821-A0AF-6C410BCCB4D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-69" yWindow="-69" windowWidth="22080" windowHeight="13132" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="1480" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mardi" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="39">
   <si>
     <t>Tâche</t>
   </si>
@@ -226,6 +226,240 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>17235</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>19958</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8083A0C-2067-42DE-B1B7-8466AB58ADB7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4138385" y="0"/>
+          <a:ext cx="3272973" cy="2419350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100"/>
+            <a:t>Colonne A : sélectionner la tâche recherchée</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100"/>
+            <a:t>Colonnes</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t> B &amp; C : entrer les heures de début et de fin du shift</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Colonne D : entrer le nombre de personnes nécessaires sans tenir compte du/de la responsable.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Répéter pour chaque shift</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Remarque: les tâches de responsables qui s'auto-gèrent (Accueil, Bourdon.ne, Horaires, Stageman, ainsi que les responsables des bars) ne doivent pas être entrés dans la liste.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>10884</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>21770</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>7257</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69B18068-D650-EB5E-F482-693B2FA92851}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1795234" y="0"/>
+          <a:ext cx="3281136" cy="1480457"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100"/>
+            <a:t>L'onglet</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t> "Tâches" contient la liste de toutes les tâches existantes à La Ruche.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="0" algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" lvl="0" indent="-171450" algn="l">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Toutes les tâches ne sont pas forcément assignées dans les plages horaires! Example : Accueil ou Bourdon.ne</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -513,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA866B2F-4C6D-48C1-B7B5-0E0D9D9973FA}">
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="16.15234375" customWidth="1"/>
@@ -535,43 +769,43 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B2" s="3">
         <v>0.66666666666666663</v>
       </c>
       <c r="C2" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" s="3">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C3" s="3">
         <v>0.79166666666666663</v>
       </c>
-      <c r="C3" s="3">
-        <v>0.91666666666666663</v>
-      </c>
       <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>36</v>
       </c>
       <c r="B4" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="C4" s="3">
-        <v>0.72916666666666663</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -582,10 +816,10 @@
         <v>36</v>
       </c>
       <c r="B5" s="3">
-        <v>0.72916666666666663</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C5" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -596,10 +830,10 @@
         <v>36</v>
       </c>
       <c r="B6" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="C6" s="3">
-        <v>0.85416666666666663</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -610,24 +844,24 @@
         <v>36</v>
       </c>
       <c r="B7" s="3">
-        <v>0.85416666666666663</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="C7" s="3">
-        <v>0.91666666666666663</v>
+        <v>1.0208333333333333</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="B8" s="3">
-        <v>0.91666666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C8" s="3">
-        <v>0.97916666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -635,16 +869,16 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="B9" s="3">
-        <v>0.97916666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="C9" s="3">
-        <v>1.0208333333333333</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -652,10 +886,10 @@
         <v>18</v>
       </c>
       <c r="B10" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="C10" s="3">
-        <v>0.75</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="D10">
         <v>3</v>
@@ -666,10 +900,10 @@
         <v>18</v>
       </c>
       <c r="B11" s="3">
-        <v>0.75</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="C11" s="3">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="D11">
         <v>3</v>
@@ -677,30 +911,30 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B12" s="3">
-        <v>0.83333333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="C12" s="3">
-        <v>0.91666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B13" s="3">
-        <v>0.91666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="C13" s="3">
-        <v>1</v>
+        <v>0.8125</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
@@ -708,10 +942,10 @@
         <v>20</v>
       </c>
       <c r="B14" s="3">
-        <v>0.6875</v>
+        <v>0.8125</v>
       </c>
       <c r="C14" s="3">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -722,10 +956,10 @@
         <v>20</v>
       </c>
       <c r="B15" s="3">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="C15" s="3">
-        <v>0.8125</v>
+        <v>0.9375</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -736,10 +970,10 @@
         <v>20</v>
       </c>
       <c r="B16" s="3">
-        <v>0.8125</v>
+        <v>0.9375</v>
       </c>
       <c r="C16" s="3">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -747,30 +981,30 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" s="3">
-        <v>0.875</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C17" s="3">
-        <v>0.9375</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" s="3">
-        <v>0.9375</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="C18" s="3">
-        <v>1</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
@@ -778,13 +1012,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="C19" s="3">
-        <v>0.72916666666666663</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
@@ -792,13 +1026,13 @@
         <v>21</v>
       </c>
       <c r="B20" s="3">
-        <v>0.72916666666666663</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C20" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
@@ -806,13 +1040,13 @@
         <v>21</v>
       </c>
       <c r="B21" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="C21" s="3">
-        <v>0.85416666666666663</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
@@ -820,52 +1054,52 @@
         <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>0.85416666666666663</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="C22" s="3">
-        <v>0.91666666666666663</v>
+        <v>1.0208333333333333</v>
       </c>
       <c r="D22">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B23" s="3">
-        <v>0.91666666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C23" s="3">
-        <v>0.97916666666666663</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B24" s="3">
-        <v>0.97916666666666663</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="C24" s="3">
-        <v>1.0208333333333333</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="B25" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="C25" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -873,10 +1107,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="B26" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C26" s="3">
         <v>0.91666666666666663</v>
@@ -887,13 +1121,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="B27" s="3">
         <v>0.91666666666666663</v>
       </c>
       <c r="C27" s="3">
-        <v>1.0208333333333333</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -904,10 +1138,10 @@
         <v>19</v>
       </c>
       <c r="B28" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="C28" s="3">
-        <v>0.72916666666666663</v>
+        <v>1.0208333333333333</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -915,13 +1149,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B29" s="3">
-        <v>0.72916666666666663</v>
+        <v>0.6875</v>
       </c>
       <c r="C29" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -929,13 +1163,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C30" s="3">
-        <v>0.85416666666666663</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -943,13 +1177,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>0.85416666666666663</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="C31" s="3">
-        <v>0.91666666666666663</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -957,13 +1191,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>0.91666666666666663</v>
+        <v>0.875</v>
       </c>
       <c r="C32" s="3">
-        <v>0.97916666666666663</v>
+        <v>0.95833333333333337</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -971,41 +1205,41 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B33" s="3">
-        <v>0.97916666666666663</v>
+        <v>0.6875</v>
       </c>
       <c r="C33" s="3">
-        <v>1.0208333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>29</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>6</v>
+        <v>31</v>
+      </c>
+      <c r="B34" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C34" s="3">
+        <v>0.89583333333333337</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>11</v>
+        <v>32</v>
+      </c>
+      <c r="B35" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="C35" s="3">
+        <v>0.77083333333333337</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1013,13 +1247,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>13</v>
+        <v>5</v>
+      </c>
+      <c r="C36" s="3">
+        <v>0.91666666666666663</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1027,13 +1261,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>4</v>
+        <v>33</v>
+      </c>
+      <c r="B37" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C37" s="3">
+        <v>0.79166666666666663</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1041,118 +1275,49 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>31</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>13</v>
+        <v>33</v>
+      </c>
+      <c r="B38" s="3">
+        <v>0.875</v>
+      </c>
+      <c r="C38" s="3">
+        <v>0.95833333333333337</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>31</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>6</v>
+        <v>34</v>
+      </c>
+      <c r="B39" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C39" s="3">
+        <v>0.79166666666666663</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>32</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>4</v>
+        <v>34</v>
+      </c>
+      <c r="B40" s="3">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C40" s="3">
+        <v>0.97916666666666663</v>
       </c>
       <c r="D40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A41" t="s">
-        <v>32</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A42" t="s">
-        <v>33</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A43" t="s">
-        <v>33</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A44" t="s">
-        <v>34</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A45" t="s">
-        <v>34</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D45">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -1160,7 +1325,7 @@
           <x14:formula1>
             <xm:f>Tâches!$A$2:$A$19</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A495</xm:sqref>
+          <xm:sqref>A2:A490</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3948,5 +4113,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/plages_horaires.xlsx
+++ b/data/plages_horaires.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sschies1\_code\1.09_VScode\06_VoeuxConcerts\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE72853-F563-4835-9D0F-03678D6E3A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B232FED-579B-4B5F-9564-FCCBE456ACDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="1480" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mardi" sheetId="2" r:id="rId1"/>
@@ -19,9 +19,9 @@
     <sheet name="Vendredi" sheetId="15" r:id="rId4"/>
     <sheet name="Samedi" sheetId="16" r:id="rId5"/>
     <sheet name="Dimanche" sheetId="17" r:id="rId6"/>
-    <sheet name="Tâches" sheetId="12" state="hidden" r:id="rId7"/>
+    <sheet name="Tâches" sheetId="12" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateCount="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="23">
   <si>
     <t>Tâche</t>
   </si>
@@ -51,15 +51,6 @@
   </si>
   <si>
     <t>Nb_personnes</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>Tech T'es rien…</t>
-  </si>
-  <si>
-    <t>Tech Muchmuche</t>
   </si>
   <si>
     <t>Tech Jacquard</t>
@@ -92,9 +83,6 @@
     <t>Déambule Goulus</t>
   </si>
   <si>
-    <t>Déambule Ko-compagnie</t>
-  </si>
-  <si>
     <t>Déambule Spoutnik</t>
   </si>
   <si>
@@ -111,6 +99,15 @@
   </si>
   <si>
     <t>Horaires</t>
+  </si>
+  <si>
+    <t>Tech Phusis</t>
+  </si>
+  <si>
+    <t>Tech T'es rien</t>
+  </si>
+  <si>
+    <t>Déambule Volkanik</t>
   </si>
 </sst>
 </file>
@@ -1427,10 +1424,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent2">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
@@ -1805,7 +1799,7 @@
     </row>
     <row r="2" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B2" s="2">
         <v>0.66666666666666663</v>
@@ -1819,7 +1813,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2">
         <v>0.72916666666666663</v>
@@ -1833,7 +1827,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2">
         <v>0.79166666666666663</v>
@@ -1847,7 +1841,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2">
         <v>0.85416666666666663</v>
@@ -1861,7 +1855,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2">
         <v>0.91666666666666663</v>
@@ -1875,7 +1869,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2">
         <v>0.97916666666666663</v>
@@ -1889,7 +1883,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2">
         <v>0.66666666666666663</v>
@@ -1903,7 +1897,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2">
         <v>0.75</v>
@@ -1917,7 +1911,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2">
         <v>0.83333333333333337</v>
@@ -1931,7 +1925,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2">
         <v>0.91666666666666663</v>
@@ -1945,7 +1939,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B12" s="2">
         <v>0.6875</v>
@@ -1959,7 +1953,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2">
         <v>0.75</v>
@@ -1973,7 +1967,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2">
         <v>0.8125</v>
@@ -1987,7 +1981,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B15" s="2">
         <v>0.875</v>
@@ -2001,7 +1995,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B16" s="2">
         <v>0.9375</v>
@@ -2015,7 +2009,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B17" s="2">
         <v>0.66666666666666663</v>
@@ -2029,7 +2023,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B18" s="2">
         <v>0.72916666666666663</v>
@@ -2043,7 +2037,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B19" s="2">
         <v>0.79166666666666663</v>
@@ -2057,7 +2051,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B20" s="2">
         <v>0.85416666666666663</v>
@@ -2071,7 +2065,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B21" s="2">
         <v>0.91666666666666663</v>
@@ -2085,7 +2079,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B22" s="2">
         <v>0.97916666666666663</v>
@@ -2099,7 +2093,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B23" s="2">
         <v>0.66666666666666663</v>
@@ -2113,7 +2107,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B24" s="2">
         <v>0.72916666666666663</v>
@@ -2127,7 +2121,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B25" s="2">
         <v>0.79166666666666663</v>
@@ -2141,7 +2135,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B26" s="2">
         <v>0.85416666666666663</v>
@@ -2155,7 +2149,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B27" s="2">
         <v>0.91666666666666663</v>
@@ -2169,7 +2163,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B28" s="2">
         <v>0.97916666666666663</v>
@@ -2183,7 +2177,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B29" s="2">
         <v>0.6875</v>
@@ -2197,7 +2191,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B30" s="2">
         <v>0.85416666666666663</v>
@@ -2211,7 +2205,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B31" s="2">
         <v>0.70833333333333337</v>
@@ -2225,7 +2219,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B32" s="2">
         <v>0.875</v>
@@ -2239,7 +2233,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B33" s="2">
         <v>0.6875</v>
@@ -2253,7 +2247,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B34" s="2">
         <v>0.83333333333333337</v>
@@ -2267,7 +2261,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B35" s="2">
         <v>0.6875</v>
@@ -2281,13 +2275,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>17</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>4</v>
+        <v>22</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0.9375</v>
       </c>
       <c r="C36" s="2">
-        <v>0.91666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -2295,7 +2289,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B37" s="2">
         <v>0.70833333333333337</v>
@@ -2309,10 +2303,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B38" s="2">
-        <v>0.875</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="C38" s="2">
         <v>0.95833333333333337</v>
@@ -2323,7 +2317,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B39" s="2">
         <v>0.70833333333333337</v>
@@ -2337,7 +2331,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B40" s="2">
         <v>0.89583333333333337</v>
@@ -3462,97 +3456,97 @@
   <sheetData>
     <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/data/plages_horaires.xlsx
+++ b/data/plages_horaires.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sschies1\_code\1.09_VScode\06_VoeuxConcerts\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B232FED-579B-4B5F-9564-FCCBE456ACDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819A4128-1418-45EB-9824-66A881C0B56B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mardi" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="26">
   <si>
     <t>Tâche</t>
   </si>
@@ -69,9 +69,6 @@
   </si>
   <si>
     <t>Bar public</t>
-  </si>
-  <si>
-    <t>Tâches</t>
   </si>
   <si>
     <t>Déambule Gerry</t>
@@ -108,6 +105,18 @@
   </si>
   <si>
     <t>Déambule Volkanik</t>
+  </si>
+  <si>
+    <t>Abeille Ruche</t>
+  </si>
+  <si>
+    <t>Abeille Entrée</t>
+  </si>
+  <si>
+    <t>Tâches spécifiques</t>
+  </si>
+  <si>
+    <t>Tâches communes</t>
   </si>
 </sst>
 </file>
@@ -1393,15 +1402,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>10884</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>21770</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>7257</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1799,7 +1808,7 @@
     </row>
     <row r="2" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2">
         <v>0.66666666666666663</v>
@@ -1813,7 +1822,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2">
         <v>0.72916666666666663</v>
@@ -1827,7 +1836,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2">
         <v>0.79166666666666663</v>
@@ -1841,7 +1850,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2">
         <v>0.85416666666666663</v>
@@ -1855,7 +1864,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2">
         <v>0.91666666666666663</v>
@@ -1869,7 +1878,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2">
         <v>0.97916666666666663</v>
@@ -2177,7 +2186,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B29" s="2">
         <v>0.6875</v>
@@ -2191,7 +2200,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B30" s="2">
         <v>0.85416666666666663</v>
@@ -2205,7 +2214,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" s="2">
         <v>0.70833333333333337</v>
@@ -2219,7 +2228,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" s="2">
         <v>0.875</v>
@@ -2233,7 +2242,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B33" s="2">
         <v>0.6875</v>
@@ -2247,7 +2256,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B34" s="2">
         <v>0.83333333333333337</v>
@@ -2261,7 +2270,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B35" s="2">
         <v>0.6875</v>
@@ -2275,7 +2284,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B36" s="2">
         <v>0.9375</v>
@@ -2289,7 +2298,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B37" s="2">
         <v>0.70833333333333337</v>
@@ -2303,7 +2312,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B38" s="2">
         <v>0.91666666666666663</v>
@@ -2317,7 +2326,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B39" s="2">
         <v>0.70833333333333337</v>
@@ -2331,7 +2340,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B40" s="2">
         <v>0.89583333333333337</v>
@@ -2360,7 +2369,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F8E24F13-6261-4BE2-B208-016A7D67164C}">
           <x14:formula1>
-            <xm:f>Tâches!$A$2:$A$19</xm:f>
+            <xm:f>Tâches!$A$2:$A$16</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A490</xm:sqref>
         </x14:dataValidation>
@@ -2575,7 +2584,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{681463FE-B2A4-41FC-B9CF-344DF7F46A27}">
           <x14:formula1>
-            <xm:f>Tâches!$A$8:$A$15</xm:f>
+            <xm:f>Tâches!$A$2:$A$12</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A36</xm:sqref>
         </x14:dataValidation>
@@ -2790,7 +2799,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1E5801FF-69D3-4F42-90AD-4F59B8D30F8C}">
           <x14:formula1>
-            <xm:f>Tâches!$A$8:$A$15</xm:f>
+            <xm:f>Tâches!$A$2:$A$12</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A36</xm:sqref>
         </x14:dataValidation>
@@ -3005,7 +3014,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B631A0C4-531A-44AB-B9EA-B7D7E31D7251}">
           <x14:formula1>
-            <xm:f>Tâches!$A$8:$A$15</xm:f>
+            <xm:f>Tâches!$A$2:$A$12</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A36</xm:sqref>
         </x14:dataValidation>
@@ -3220,7 +3229,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{47D4686B-0097-4A47-95B0-E31D35A9D5B5}">
           <x14:formula1>
-            <xm:f>Tâches!$A$8:$A$15</xm:f>
+            <xm:f>Tâches!$A$2:$A$12</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A36</xm:sqref>
         </x14:dataValidation>
@@ -3435,7 +3444,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D59E45ED-DF26-42E3-B55D-A2C4762E6F3A}">
           <x14:formula1>
-            <xm:f>Tâches!$A$8:$A$15</xm:f>
+            <xm:f>Tâches!$A$2:$A$12</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A36</xm:sqref>
         </x14:dataValidation>
@@ -3448,105 +3457,102 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B30C51F-AE90-4524-AE2A-6A9EE13EB899}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="25.23046875" customWidth="1"/>
+    <col min="1" max="2" width="25.23046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+        <v>25</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
